--- a/Result/profitability/2432.xlsx
+++ b/Result/profitability/2432.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM22"/>
+  <dimension ref="A1:AM23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.22</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5662499999999999</v>
+        <v>0.5825</v>
       </c>
       <c r="N2" t="n">
-        <v>15.46625</v>
+        <v>15.1475</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.44</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5675</v>
+        <v>0.5475000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>18.51875</v>
+        <v>18</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -3224,6 +3224,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2432</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1296</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1161</v>
+      </c>
+      <c r="E23" t="n">
+        <v>135</v>
+      </c>
+      <c r="F23" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="G23" t="n">
+        <v>20</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>1.58%</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>20</v>
+      </c>
+      <c r="J23" t="n">
+        <v>40</v>
+      </c>
+      <c r="K23" t="n">
+        <v>35</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.48375</v>
+      </c>
+      <c r="N23" t="n">
+        <v>12.4225</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.153846153846154</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>-0.5199999999999996</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-0.04761904761904756</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>-1.219999999999999</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>-0.1049913941480206</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK23" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
